--- a/xlsx/Power/p14.xlsx
+++ b/xlsx/Power/p14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5E3893-8252-4E9F-AE55-5235213F2D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A0039A-B470-41DE-8C50-1DC3B9E221C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{45E87EAF-CE81-48F7-9001-618CEB4B3278}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{45E87EAF-CE81-48F7-9001-618CEB4B3278}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
         <v>1</v>
       </c>
       <c r="C1">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="D1">
         <v>1</v>
@@ -436,7 +436,7 @@
         <v>0.999</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.86099999999999999</v>
+        <v>0.876</v>
       </c>
       <c r="B4">
         <v>0.997</v>
@@ -596,7 +596,7 @@
         <v>0.93100000000000005</v>
       </c>
       <c r="C7">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="D7">
         <v>0.999</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.91200000000000003</v>
       </c>
       <c r="C9">
-        <v>0.88100000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="D9">
-        <v>0.83499999999999996</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0.875</v>
+        <v>0.999</v>
       </c>
       <c r="F9">
-        <v>0.92900000000000005</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="G9">
-        <v>0.96699999999999997</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H9">
-        <v>0.98899999999999999</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="I9">
         <v>0.99299999999999999</v>
       </c>
       <c r="J9">
-        <v>0.995</v>
+        <v>0.997</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p14.xlsx
+++ b/xlsx/Power/p14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A0039A-B470-41DE-8C50-1DC3B9E221C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024F928B-7B15-4248-B9E9-BDB93BDDE594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{45E87EAF-CE81-48F7-9001-618CEB4B3278}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{45E87EAF-CE81-48F7-9001-618CEB4B3278}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
         <v>1</v>
       </c>
       <c r="C1">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="D1">
         <v>1</v>
@@ -436,7 +436,7 @@
         <v>0.999</v>
       </c>
       <c r="C2">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.876</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="B4">
         <v>0.997</v>
@@ -596,7 +596,7 @@
         <v>0.93100000000000005</v>
       </c>
       <c r="C7">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="D7">
         <v>0.999</v>
@@ -628,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.91200000000000003</v>
       </c>
       <c r="C9">
-        <v>0.996</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="E9">
-        <v>0.999</v>
+        <v>0.875</v>
       </c>
       <c r="F9">
-        <v>0.98799999999999999</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="G9">
-        <v>0.98399999999999999</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="H9">
-        <v>0.99399999999999999</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="I9">
         <v>0.99299999999999999</v>
       </c>
       <c r="J9">
-        <v>0.997</v>
+        <v>0.995</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p14.xlsx
+++ b/xlsx/Power/p14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024F928B-7B15-4248-B9E9-BDB93BDDE594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCB36BF-6F09-4579-BD43-553CAE40E6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{45E87EAF-CE81-48F7-9001-618CEB4B3278}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{45E87EAF-CE81-48F7-9001-618CEB4B3278}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -430,7 +430,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.86599999999999999</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="B2">
         <v>0.999</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.88100000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="B3">
         <v>0.998</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.86099999999999999</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="B4">
         <v>0.997</v>
@@ -526,16 +526,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>9.4E-2</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.71299999999999997</v>
+        <v>0.71</v>
       </c>
       <c r="B6">
         <v>0.95899999999999996</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.67400000000000004</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="B7">
         <v>0.93100000000000005</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>0.89200000000000002</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -654,22 +654,22 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.59499999999999997</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="B9">
-        <v>0.91200000000000003</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="C9">
-        <v>0.88100000000000001</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="D9">
-        <v>0.83499999999999996</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="E9">
-        <v>0.875</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="F9">
-        <v>0.92900000000000005</v>
+        <v>0.93</v>
       </c>
       <c r="G9">
         <v>0.96699999999999997</v>
@@ -681,7 +681,7 @@
         <v>0.99299999999999999</v>
       </c>
       <c r="J9">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
     </row>
   </sheetData>
